--- a/examples/extensions/thai_bim/examples/stair-Floating-BBS.xlsx
+++ b/examples/extensions/thai_bim/examples/stair-Floating-BBS.xlsx
@@ -213,7 +213,7 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -395,7 +395,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O11" s="0" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O12" s="0" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="N13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O13" s="0" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O14" s="0" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="N15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O15" s="0" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="N16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O16" s="0" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="O17" s="0" t="inlineStr">
@@ -1694,12 +1694,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f633a46bca349ac</t>
+          <t xml:space="preserve">efa30b5625da4b57</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -1752,12 +1752,12 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5e0be38754a04822</t>
+          <t xml:space="preserve">b0da3ab30f244e39</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">656118cbc92d469b</t>
+          <t xml:space="preserve">895c7f9f03594c97</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8586200ec054ece</t>
+          <t xml:space="preserve">eff0da4d061c4100</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1926,12 +1926,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c9700431c47e49ee</t>
+          <t xml:space="preserve">348ad3dd685d4eec</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8abcf7dea4984455</t>
+          <t xml:space="preserve">1de2fed8f6844c08</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -2042,12 +2042,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">91e7132f7d2d49b9</t>
+          <t xml:space="preserve">a5baaa9eebd349eb</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">53eb133f79314bc8</t>
+          <t xml:space="preserve">1cb3763e7bb2475b</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e002e0145ad8472b</t>
+          <t xml:space="preserve">1a72bfabb04b413d</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -2216,12 +2216,12 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">34f9c919d9794616</t>
+          <t xml:space="preserve">b8902b957a2549e5</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -2274,12 +2274,12 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">924ed9cc297a40d6</t>
+          <t xml:space="preserve">7fd05de125ff4a48</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -2332,12 +2332,12 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">dfad8abf8a4a4205</t>
+          <t xml:space="preserve">1b6a4be4c1114179</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -2390,12 +2390,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">78d12a1057e34791</t>
+          <t xml:space="preserve">aeabce31317c4fbd</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -2448,12 +2448,12 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">22a507403b794961</t>
+          <t xml:space="preserve">8598b40c11894d41</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -2506,12 +2506,12 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7c826e57d3944fb4</t>
+          <t xml:space="preserve">46b95d4dd29f46f2</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -2564,12 +2564,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">632c68bfde7547a8</t>
+          <t xml:space="preserve">c2d3a28750ab4c5d</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2622,12 +2622,12 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1ad934fed7e4b98</t>
+          <t xml:space="preserve">9f34c938dba14e88</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3231e4d9c4164684</t>
+          <t xml:space="preserve">98c47370364644c9</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2738,12 +2738,12 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cbaa42eae6a94e5d</t>
+          <t xml:space="preserve">09a96929cc0345e5</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -2796,12 +2796,12 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3bcf0a24dc9f459b</t>
+          <t xml:space="preserve">940e7bbc5985487b</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2608232c44284375</t>
+          <t xml:space="preserve">4d0473831b0145d1</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -2912,12 +2912,12 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">048bf24b1f764cf0</t>
+          <t xml:space="preserve">fc7c349917de4539</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -2970,12 +2970,12 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6d6046b9938447bc</t>
+          <t xml:space="preserve">330ce954ae9141a4</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -3028,12 +3028,12 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b79b171d051f49d7</t>
+          <t xml:space="preserve">e1040354a05143b7</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -3086,12 +3086,12 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291f693714d4ab8</t>
+          <t xml:space="preserve">421aa332229b4bfb</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -3144,12 +3144,12 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c7191fd13c5b466b</t>
+          <t xml:space="preserve">bd58b96c5e624ac4</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -3202,12 +3202,12 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">69e638d4341e44f5</t>
+          <t xml:space="preserve">8f874199951a4929</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1702c74364f249ab</t>
+          <t xml:space="preserve">24220ed738a74fe8</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -3318,12 +3318,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b866a251107f4937</t>
+          <t xml:space="preserve">0a98526cf93343b5</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3376,12 +3376,12 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">77279da9a6e54454</t>
+          <t xml:space="preserve">772488d249d846b1</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -3434,12 +3434,12 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ef86080a6a7e4512</t>
+          <t xml:space="preserve">920dfbf0a266499e</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -3492,12 +3492,12 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fdaaa51c1ddb4d21</t>
+          <t xml:space="preserve">67da29aa57d343bd</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -3550,12 +3550,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6e79ec8fff74efb</t>
+          <t xml:space="preserve">ab0a3902d8b54607</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -3608,12 +3608,12 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5de3eb8eef774dae</t>
+          <t xml:space="preserve">c63dcf1ef18a4e9c</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -3666,12 +3666,12 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">00303221b256488f</t>
+          <t xml:space="preserve">834a017fd9b84961</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -3724,12 +3724,12 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ff2524092db84b83</t>
+          <t xml:space="preserve">7ab79d3740e44cb4</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c3ba780a25da4c89</t>
+          <t xml:space="preserve">8d1bcf1ddd074828</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -3840,12 +3840,12 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">da69aa1d65e54f28</t>
+          <t xml:space="preserve">240a3a66027745d7</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -3898,12 +3898,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c87657d01ede4b78</t>
+          <t xml:space="preserve">0912f6acc15440c8</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3b6f294f60274043</t>
+          <t xml:space="preserve">7752bee61f004b60</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -4014,12 +4014,12 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8c248f4715d841f8</t>
+          <t xml:space="preserve">2c1867c0ed174223</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -4072,12 +4072,12 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">026825dd2fc2414b</t>
+          <t xml:space="preserve">3fa077a68def4a75</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -4130,12 +4130,12 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a592e9b94bc54806</t>
+          <t xml:space="preserve">ad05248c860b4ae7</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -4188,12 +4188,12 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">32a1128ec6654759</t>
+          <t xml:space="preserve">13b0b43c29bf4b9b</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -4246,12 +4246,12 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2c56816d112642a6</t>
+          <t xml:space="preserve">101e9c9eb2f04ca0</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -4304,12 +4304,12 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">caf3053694064279</t>
+          <t xml:space="preserve">031bff9ecd5e4c85</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -4362,12 +4362,12 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e18c047bc1214c20</t>
+          <t xml:space="preserve">759bdad7f47641e6</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -4420,12 +4420,12 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c7b391e9b1b14fe8</t>
+          <t xml:space="preserve">d6ec571c95f24953</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -4478,12 +4478,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">31b5a354f6264ed4</t>
+          <t xml:space="preserve">1b71526607964b06</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -4536,12 +4536,12 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fb98ad43542c4323</t>
+          <t xml:space="preserve">760a7ee7e9654d11</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -4594,12 +4594,12 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">dcb4937c7f994285</t>
+          <t xml:space="preserve">ac14049185cf41e7</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6fda6ed7899f4df3</t>
+          <t xml:space="preserve">4636e7419f56434b</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -4710,12 +4710,12 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">107bcaaa718a44c9</t>
+          <t xml:space="preserve">3e43194c535845bf</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -4768,12 +4768,12 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc2c180bbcda40e0</t>
+          <t xml:space="preserve">1854927777c344db</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -4826,12 +4826,12 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">486554acd6cd4529</t>
+          <t xml:space="preserve">23539d6df00a4bac</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -4884,12 +4884,12 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900e10fa4bd4052</t>
+          <t xml:space="preserve">072bfabaa9e648dc</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -4942,12 +4942,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">572363fe58b84531</t>
+          <t xml:space="preserve">1b112015c86e4c22</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5000,12 +5000,12 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cbb31ff093a643c6</t>
+          <t xml:space="preserve">70f8c4935c314609</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5058,12 +5058,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3e94cc94a65f4160</t>
+          <t xml:space="preserve">a60223f577a64775</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">50fcd448e2fe478b</t>
+          <t xml:space="preserve">9593e895f93f4e44</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4d9d470438d34cfe</t>
+          <t xml:space="preserve">5b8a953c123d47e6</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -5232,12 +5232,12 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5264ccde431d452e</t>
+          <t xml:space="preserve">a94e8727d5f84d5d</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -5290,12 +5290,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">504c6a6f6fd44334</t>
+          <t xml:space="preserve">aa067cef130d4575</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -5348,12 +5348,12 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d1c75bd999a43f1</t>
+          <t xml:space="preserve">062c0731190d4a61</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -5406,12 +5406,12 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9122ddfa3f5e4237</t>
+          <t xml:space="preserve">92593eaf03754545</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -5464,12 +5464,12 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">40a0ece46b774678</t>
+          <t xml:space="preserve">5242f6d0172c43e8</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -5522,12 +5522,12 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">41f365a6b549433e</t>
+          <t xml:space="preserve">27b627415ae24c17</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -5580,12 +5580,12 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d8475d0511b649cc</t>
+          <t xml:space="preserve">9e8da2a4cdd7451b</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -5638,12 +5638,12 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1efc4766aab4ffa</t>
+          <t xml:space="preserve">c5c3812796754404</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -5696,12 +5696,12 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9f0196a70f134a99</t>
+          <t xml:space="preserve">39f7935f882e4706</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -5754,12 +5754,12 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">edbef4afc7b5462c</t>
+          <t xml:space="preserve">b44bf93adbf14bbf</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -5812,12 +5812,12 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9fa60c7f99f445dd</t>
+          <t xml:space="preserve">40f8643b05844259</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1f543dbc52134c75</t>
+          <t xml:space="preserve">1300da7124204351</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
